--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205B0A43-CF66-42FB-9531-076E0C8E6A75}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE80EF0-444B-4340-88FB-CB4B0054CC86}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -479,6 +479,10 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -488,10 +492,6 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1048,13 +1048,13 @@
       <c r="F9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="42" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="45" t="s">
+      <c r="I9" s="42" t="s">
         <v>19</v>
       </c>
       <c r="J9" s="14" t="s">
@@ -1122,12 +1122,22 @@
       <c r="B11" s="27">
         <v>46175</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
+      <c r="C11" s="32">
+        <v>242753</v>
+      </c>
+      <c r="D11" s="32">
+        <v>207146</v>
+      </c>
       <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
+      <c r="F11" s="32">
+        <v>118</v>
+      </c>
+      <c r="G11" s="31">
+        <v>42</v>
+      </c>
+      <c r="H11" s="32">
+        <v>207264</v>
+      </c>
       <c r="I11" s="31"/>
       <c r="J11" s="32"/>
       <c r="K11" s="31"/>
@@ -1262,17 +1272,17 @@
       <c r="B16" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="44"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="46"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -1432,15 +1442,15 @@
       <c r="B22" s="27">
         <v>46186</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="46"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -1460,17 +1470,17 @@
       <c r="B23" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="44"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="46"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="7"/>
@@ -1578,9 +1588,9 @@
       <c r="D27" s="37"/>
       <c r="E27" s="13"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="46"/>
+      <c r="G27" s="43"/>
       <c r="H27" s="33"/>
-      <c r="I27" s="46"/>
+      <c r="I27" s="43"/>
       <c r="J27" s="33"/>
       <c r="K27" s="30"/>
       <c r="L27" s="1"/>
@@ -1606,9 +1616,9 @@
       <c r="D28" s="37"/>
       <c r="E28" s="13"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="46"/>
+      <c r="G28" s="43"/>
       <c r="H28" s="33"/>
-      <c r="I28" s="46"/>
+      <c r="I28" s="43"/>
       <c r="J28" s="33"/>
       <c r="K28" s="30"/>
       <c r="L28" s="1"/>
@@ -1634,9 +1644,9 @@
       <c r="D29" s="37"/>
       <c r="E29" s="13"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="46"/>
+      <c r="G29" s="43"/>
       <c r="H29" s="33"/>
-      <c r="I29" s="46"/>
+      <c r="I29" s="43"/>
       <c r="J29" s="33"/>
       <c r="K29" s="30"/>
       <c r="L29" s="1"/>
@@ -1658,17 +1668,17 @@
       <c r="B30" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="42" t="s">
+      <c r="C30" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="44"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="46"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="7"/>
@@ -1692,9 +1702,9 @@
       <c r="D31" s="37"/>
       <c r="E31" s="13"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="46"/>
+      <c r="G31" s="43"/>
       <c r="H31" s="33"/>
-      <c r="I31" s="46"/>
+      <c r="I31" s="43"/>
       <c r="J31" s="33"/>
       <c r="K31" s="30"/>
       <c r="L31" s="1"/>
@@ -1832,9 +1842,9 @@
       <c r="D36" s="38"/>
       <c r="E36" s="13"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="46"/>
+      <c r="G36" s="43"/>
       <c r="H36" s="33"/>
-      <c r="I36" s="46"/>
+      <c r="I36" s="43"/>
       <c r="J36" s="33"/>
       <c r="K36" s="30"/>
       <c r="L36" s="1"/>
@@ -1856,17 +1866,17 @@
       <c r="B37" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C37" s="42" t="s">
+      <c r="C37" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="44"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="46"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="8"/>
@@ -1986,15 +1996,15 @@
     <row r="42" spans="1:22" ht="15">
       <c r="A42" s="21"/>
       <c r="B42" s="35"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="44"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="46"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="7"/>
@@ -2013,35 +2023,35 @@
       </c>
       <c r="B43" s="27"/>
       <c r="C43" s="16">
-        <f>SUM(C10:C42)</f>
-        <v>475222.5</v>
+        <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
+        <v>717975.5</v>
       </c>
       <c r="D43" s="16">
-        <f>SUM(D10:D42)</f>
-        <v>486611.75</v>
+        <f t="shared" si="0"/>
+        <v>693757.75</v>
       </c>
       <c r="E43" s="28">
-        <f>SUM(E10:E42)</f>
+        <f t="shared" si="0"/>
         <v>710.75</v>
       </c>
       <c r="F43" s="16">
-        <f>SUM(F10:F42)</f>
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
+      <c r="G43" s="28">
+        <f t="shared" si="0"/>
+        <v>2802</v>
+      </c>
+      <c r="H43" s="16">
+        <f t="shared" si="0"/>
+        <v>693165</v>
+      </c>
+      <c r="I43" s="28">
+        <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="28">
-        <f>SUM(G10:G42)</f>
-        <v>2760</v>
-      </c>
-      <c r="H43" s="16">
-        <f>SUM(H10:H42)</f>
-        <v>485901</v>
-      </c>
-      <c r="I43" s="28">
-        <f t="shared" ref="I43:J43" si="0">SUM(I10:I42)</f>
-        <v>0</v>
-      </c>
       <c r="J43" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>68780</v>
       </c>
       <c r="K43" s="16">
@@ -6277,13 +6287,13 @@
       <c r="F9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="42" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="45" t="s">
+      <c r="I9" s="42" t="s">
         <v>20</v>
       </c>
       <c r="J9" s="14" t="s">
@@ -6349,12 +6359,22 @@
       <c r="B11" s="27">
         <v>46175</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="31"/>
+      <c r="C11" s="32">
+        <v>256886</v>
+      </c>
+      <c r="D11" s="32">
+        <v>217049</v>
+      </c>
+      <c r="E11" s="31">
+        <v>215</v>
+      </c>
       <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
+      <c r="G11" s="31">
+        <v>1944</v>
+      </c>
+      <c r="H11" s="32">
+        <v>216834</v>
+      </c>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
       <c r="K11" s="31"/>
@@ -6489,17 +6509,17 @@
       <c r="B16" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="44"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="46"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -6659,15 +6679,15 @@
       <c r="B22" s="27">
         <v>46186</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="46"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -6687,17 +6707,17 @@
       <c r="B23" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="44"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="46"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="7"/>
@@ -6885,17 +6905,17 @@
       <c r="B30" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="42" t="s">
+      <c r="C30" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="44"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="46"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="7"/>
@@ -7083,17 +7103,17 @@
       <c r="B37" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C37" s="42" t="s">
+      <c r="C37" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="44"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="46"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="8"/>
@@ -7213,15 +7233,15 @@
     <row r="42" spans="1:22" ht="15">
       <c r="A42" s="21"/>
       <c r="B42" s="35"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="44"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="46"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="7"/>
@@ -7240,35 +7260,35 @@
       </c>
       <c r="B43" s="27"/>
       <c r="C43" s="16">
-        <f>SUM(C10:C42)</f>
-        <v>247146</v>
+        <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
+        <v>504032</v>
       </c>
       <c r="D43" s="16">
-        <f>SUM(D10:D42)</f>
-        <v>210265.75</v>
+        <f t="shared" si="0"/>
+        <v>427314.75</v>
       </c>
       <c r="E43" s="28">
-        <f>SUM(E10:E42)</f>
-        <v>175.75</v>
+        <f t="shared" si="0"/>
+        <v>390.75</v>
       </c>
       <c r="F43" s="16">
-        <f>SUM(F10:F42)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G43" s="28">
-        <f>SUM(G10:G42)</f>
-        <v>696</v>
+        <f t="shared" si="0"/>
+        <v>2640</v>
       </c>
       <c r="H43" s="16">
-        <f>SUM(H10:H42)</f>
-        <v>210092</v>
+        <f t="shared" si="0"/>
+        <v>426926</v>
       </c>
       <c r="I43" s="28">
-        <f t="shared" ref="I43:J43" si="0">SUM(I10:I42)</f>
+        <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
         <v>0</v>
       </c>
       <c r="J43" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K43" s="16">
@@ -11503,13 +11523,13 @@
       <c r="F9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="42" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="45" t="s">
+      <c r="I9" s="42" t="s">
         <v>20</v>
       </c>
       <c r="J9" s="14" t="s">
@@ -11575,15 +11595,28 @@
       <c r="B11" s="27">
         <v>46175</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="31"/>
+      <c r="C11" s="32">
+        <v>403944</v>
+      </c>
+      <c r="D11" s="32">
+        <v>330400.75</v>
+      </c>
+      <c r="E11" s="31">
+        <v>623.75</v>
+      </c>
       <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
+      <c r="G11" s="31">
+        <f>918</f>
+        <v>918</v>
+      </c>
+      <c r="H11" s="32">
+        <v>329777</v>
+      </c>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
-      <c r="K11" s="31"/>
+      <c r="K11" s="34">
+        <v>50</v>
+      </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -11715,17 +11748,17 @@
       <c r="B16" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="44"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="45"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="46"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -11885,15 +11918,15 @@
       <c r="B22" s="27">
         <v>46186</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="46"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -11913,17 +11946,17 @@
       <c r="B23" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="44"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="46"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="7"/>
@@ -12111,17 +12144,17 @@
       <c r="B30" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="42" t="s">
+      <c r="C30" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="44"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="46"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="7"/>
@@ -12309,17 +12342,17 @@
       <c r="B37" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C37" s="42" t="s">
+      <c r="C37" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="44"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="46"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="8"/>
@@ -12439,15 +12472,15 @@
     <row r="42" spans="1:22" ht="15">
       <c r="A42" s="21"/>
       <c r="B42" s="35"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="44"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="46"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="7"/>
@@ -12466,40 +12499,40 @@
       </c>
       <c r="B43" s="27"/>
       <c r="C43" s="16">
-        <f>SUM(C10:C42)</f>
-        <v>266056</v>
+        <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
+        <v>670000</v>
       </c>
       <c r="D43" s="16">
-        <f>SUM(D10:D42)</f>
-        <v>206692</v>
+        <f t="shared" si="0"/>
+        <v>537092.75</v>
       </c>
       <c r="E43" s="28">
-        <f>SUM(E10:E42)</f>
-        <v>6000</v>
+        <f t="shared" si="0"/>
+        <v>6623.75</v>
       </c>
       <c r="F43" s="16">
-        <f>SUM(F10:F42)</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="28">
-        <f>SUM(G10:G42)</f>
-        <v>1092</v>
-      </c>
-      <c r="H43" s="16">
-        <f>SUM(H10:H42)</f>
-        <v>200692</v>
-      </c>
-      <c r="I43" s="16">
-        <f t="shared" ref="I43:J43" si="0">SUM(I10:I42)</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="G43" s="28">
+        <f t="shared" si="0"/>
+        <v>2010</v>
+      </c>
+      <c r="H43" s="16">
+        <f t="shared" si="0"/>
+        <v>530469</v>
+      </c>
+      <c r="I43" s="16">
+        <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE80EF0-444B-4340-88FB-CB4B0054CC86}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093D6656-452B-4DB7-A854-E4533233336F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -65,6 +65,56 @@
           </rPr>
           <t xml:space="preserve">
 SOUND CHECK</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{23E3D51F-92F5-4A2F-B8A3-FB24079ADD1C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+BALWARTE
+S.I. NO. 10843</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{FE4B4EC7-5870-4A20-B3D2-51E46B83AAED}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+BALWARTE
+S.I. NO. 10547</t>
         </r>
       </text>
     </comment>
@@ -188,7 +238,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,6 +350,19 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1160,14 +1223,28 @@
       <c r="B12" s="27">
         <v>46176</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
+      <c r="C12" s="32">
+        <v>361570</v>
+      </c>
+      <c r="D12" s="32">
+        <v>307410.5</v>
+      </c>
+      <c r="E12" s="31">
+        <v>1277.5</v>
+      </c>
       <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
+      <c r="G12" s="31">
+        <v>1944</v>
+      </c>
+      <c r="H12" s="32">
+        <v>306133</v>
+      </c>
+      <c r="I12" s="31">
+        <v>88549</v>
+      </c>
+      <c r="J12" s="32">
+        <v>78233</v>
+      </c>
       <c r="K12" s="31"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -2024,15 +2101,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>717975.5</v>
+        <v>1079545.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>693757.75</v>
+        <v>1001168.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>710.75</v>
+        <v>1988.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2040,19 +2117,19 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>2802</v>
+        <v>4746</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>693165</v>
+        <v>999298</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>0</v>
+        <v>88549</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>68780</v>
+        <v>147013</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093D6656-452B-4DB7-A854-E4533233336F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D2160F-37CB-4821-BC38-D0AF9206D2DE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1265,13 +1265,25 @@
       <c r="B13" s="27">
         <v>46177</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="31"/>
+      <c r="C13" s="32">
+        <v>508853</v>
+      </c>
+      <c r="D13" s="32">
+        <v>361302.25</v>
+      </c>
+      <c r="E13" s="31">
+        <v>734.25</v>
+      </c>
       <c r="F13" s="32"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="31"/>
+      <c r="G13" s="31">
+        <v>3042</v>
+      </c>
+      <c r="H13" s="34">
+        <v>360568</v>
+      </c>
+      <c r="I13" s="31">
+        <v>62272</v>
+      </c>
       <c r="J13" s="34"/>
       <c r="K13" s="32"/>
       <c r="L13" s="1"/>
@@ -2101,15 +2113,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1079545.5</v>
+        <v>1588398.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1001168.25</v>
+        <v>1362470.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>1988.25</v>
+        <v>2722.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2117,15 +2129,15 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>4746</v>
+        <v>7788</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>999298</v>
+        <v>1359866</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>88549</v>
+        <v>150821</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
@@ -6502,12 +6514,22 @@
       <c r="B13" s="27">
         <v>46177</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="31"/>
+      <c r="C13" s="32">
+        <v>248406</v>
+      </c>
+      <c r="D13" s="32">
+        <v>205139.25</v>
+      </c>
+      <c r="E13" s="31">
+        <v>48.25</v>
+      </c>
       <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="34"/>
+      <c r="G13" s="31">
+        <v>1896</v>
+      </c>
+      <c r="H13" s="34">
+        <v>205091</v>
+      </c>
       <c r="I13" s="34"/>
       <c r="J13" s="34"/>
       <c r="K13" s="32"/>
@@ -7338,15 +7360,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>504032</v>
+        <v>752438</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>427314.75</v>
+        <v>632454</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>390.75</v>
+        <v>439</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7354,11 +7376,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>2640</v>
+        <v>4536</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>426926</v>
+        <v>632017</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11741,12 +11763,22 @@
       <c r="B13" s="27">
         <v>46177</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="31"/>
+      <c r="C13" s="32">
+        <v>582314</v>
+      </c>
+      <c r="D13" s="32">
+        <v>491387</v>
+      </c>
+      <c r="E13" s="31">
+        <v>337</v>
+      </c>
       <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="34"/>
+      <c r="G13" s="31">
+        <v>1230</v>
+      </c>
+      <c r="H13" s="34">
+        <v>491050</v>
+      </c>
       <c r="I13" s="34"/>
       <c r="J13" s="34"/>
       <c r="K13" s="32"/>
@@ -12577,15 +12609,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>670000</v>
+        <v>1252314</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>537092.75</v>
+        <v>1028479.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>6623.75</v>
+        <v>6960.75</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -12593,11 +12625,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>2010</v>
+        <v>3240</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>530469</v>
+        <v>1021519</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D2160F-37CB-4821-BC38-D0AF9206D2DE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706A6210-4591-4CAA-9E12-6A4D720EEC9B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JUNE, SRS R1" sheetId="6" r:id="rId1"/>
@@ -118,12 +118,37 @@
         </r>
       </text>
     </comment>
+    <comment ref="J15" authorId="0" shapeId="0" xr:uid="{867EA403-261B-4920-809A-F301CCEA5C4C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+SI NO. 10850</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="23">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -228,6 +253,9 @@
   </si>
   <si>
     <t>TOTAL REM.</t>
+  </si>
+  <si>
+    <t>NO TRIP</t>
   </si>
 </sst>
 </file>
@@ -1305,15 +1333,17 @@
       <c r="B14" s="27">
         <v>46178</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="31"/>
+      <c r="C14" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="46"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -1333,14 +1363,16 @@
       <c r="B15" s="27">
         <v>46179</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
       <c r="E15" s="31"/>
       <c r="F15" s="31"/>
       <c r="G15" s="31"/>
-      <c r="H15" s="34"/>
+      <c r="H15" s="31"/>
       <c r="I15" s="31"/>
-      <c r="J15" s="34"/>
+      <c r="J15" s="34">
+        <v>62272</v>
+      </c>
       <c r="K15" s="32"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2141,7 +2173,7 @@
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>147013</v>
+        <v>209285</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
@@ -6144,7 +6176,8 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="C14:K14"/>
     <mergeCell ref="C30:K30"/>
     <mergeCell ref="C37:K37"/>
     <mergeCell ref="C42:K42"/>
@@ -6552,12 +6585,22 @@
       <c r="B14" s="27">
         <v>46178</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
+      <c r="C14" s="32">
+        <v>302509</v>
+      </c>
+      <c r="D14" s="32">
+        <v>261479.5</v>
+      </c>
       <c r="E14" s="31"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="34"/>
+      <c r="F14" s="32">
+        <v>62.5</v>
+      </c>
+      <c r="G14" s="32">
+        <v>1296</v>
+      </c>
+      <c r="H14" s="34">
+        <v>261542</v>
+      </c>
       <c r="I14" s="34"/>
       <c r="J14" s="34"/>
       <c r="K14" s="31"/>
@@ -6580,15 +6623,17 @@
       <c r="B15" s="27">
         <v>46179</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="32"/>
+      <c r="C15" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="46"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -7360,11 +7405,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>752438</v>
+        <v>1054947</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>632454</v>
+        <v>893933.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -7372,15 +7417,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>4536</v>
+        <v>5832</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>632017</v>
+        <v>893559</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11391,7 +11436,8 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="C15:K15"/>
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C23:K23"/>
     <mergeCell ref="C16:K16"/>
@@ -11801,12 +11847,22 @@
       <c r="B14" s="27">
         <v>46178</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="31"/>
+      <c r="C14" s="32">
+        <v>357319</v>
+      </c>
+      <c r="D14" s="32">
+        <v>303847</v>
+      </c>
+      <c r="E14" s="31">
+        <v>882</v>
+      </c>
       <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="34"/>
+      <c r="G14" s="31">
+        <v>1092</v>
+      </c>
+      <c r="H14" s="34">
+        <v>302965</v>
+      </c>
       <c r="I14" s="34"/>
       <c r="J14" s="34"/>
       <c r="K14" s="31"/>
@@ -11829,15 +11885,17 @@
       <c r="B15" s="27">
         <v>46179</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="32"/>
+      <c r="C15" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="46"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -12609,15 +12667,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1252314</v>
+        <v>1609633</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1028479.75</v>
+        <v>1332326.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>6960.75</v>
+        <v>7842.75</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -12625,11 +12683,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>3240</v>
+        <v>4332</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1021519</v>
+        <v>1324484</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -16640,7 +16698,8 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="C15:K15"/>
     <mergeCell ref="C16:K16"/>
     <mergeCell ref="C23:K23"/>
     <mergeCell ref="C30:K30"/>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706A6210-4591-4CAA-9E12-6A4D720EEC9B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546BFBF2-9D44-40E1-8C09-B26021B3A495}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="23">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1423,15 +1423,17 @@
       <c r="B17" s="27">
         <v>46181</v>
       </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="31"/>
+      <c r="C17" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="46"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -6176,7 +6178,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C30:K30"/>
     <mergeCell ref="C37:K37"/>
@@ -6184,6 +6186,7 @@
     <mergeCell ref="C16:K16"/>
     <mergeCell ref="C22:K22"/>
     <mergeCell ref="C23:K23"/>
+    <mergeCell ref="C17:K17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6683,12 +6686,22 @@
       <c r="B17" s="27">
         <v>46181</v>
       </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="31"/>
+      <c r="C17" s="32">
+        <v>379695</v>
+      </c>
+      <c r="D17" s="32">
+        <v>320595</v>
+      </c>
+      <c r="E17" s="31">
+        <v>1549</v>
+      </c>
       <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="34"/>
+      <c r="G17" s="31">
+        <v>2832</v>
+      </c>
+      <c r="H17" s="34">
+        <v>319046</v>
+      </c>
       <c r="I17" s="34"/>
       <c r="J17" s="34"/>
       <c r="K17" s="31"/>
@@ -7405,15 +7418,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1054947</v>
+        <v>1434642</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>893933.5</v>
+        <v>1214528.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>439</v>
+        <v>1988</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7421,11 +7434,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>5832</v>
+        <v>8664</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>893559</v>
+        <v>1212605</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11945,12 +11958,22 @@
       <c r="B17" s="27">
         <v>46181</v>
       </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="31"/>
+      <c r="C17" s="32">
+        <v>389426</v>
+      </c>
+      <c r="D17" s="32">
+        <v>330258.5</v>
+      </c>
+      <c r="E17" s="31">
+        <v>7491.5</v>
+      </c>
       <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="34"/>
+      <c r="G17" s="31">
+        <v>2478</v>
+      </c>
+      <c r="H17" s="34">
+        <v>322767</v>
+      </c>
       <c r="I17" s="34"/>
       <c r="J17" s="34"/>
       <c r="K17" s="31"/>
@@ -12667,15 +12690,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1609633</v>
+        <v>1999059</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1332326.75</v>
+        <v>1662585.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>7842.75</v>
+        <v>15334.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -12683,11 +12706,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>4332</v>
+        <v>6810</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1324484</v>
+        <v>1647251</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -16699,13 +16722,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="C42:K42"/>
+    <mergeCell ref="C22:K22"/>
     <mergeCell ref="C15:K15"/>
     <mergeCell ref="C16:K16"/>
     <mergeCell ref="C23:K23"/>
     <mergeCell ref="C30:K30"/>
     <mergeCell ref="C37:K37"/>
-    <mergeCell ref="C42:K42"/>
-    <mergeCell ref="C22:K22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546BFBF2-9D44-40E1-8C09-B26021B3A495}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710396EA-2F0B-4852-8B0B-C8799F5BFC12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -148,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="23">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1453,12 +1453,20 @@
       <c r="B18" s="27">
         <v>46182</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
+      <c r="C18" s="32">
+        <v>284998</v>
+      </c>
+      <c r="D18" s="32">
+        <v>249779.5</v>
+      </c>
+      <c r="E18" s="31">
+        <v>351.5</v>
+      </c>
       <c r="F18" s="31"/>
       <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
+      <c r="H18" s="32">
+        <v>249428</v>
+      </c>
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
       <c r="K18" s="31"/>
@@ -1481,12 +1489,20 @@
       <c r="B19" s="27">
         <v>46183</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
+      <c r="C19" s="34">
+        <v>262429</v>
+      </c>
+      <c r="D19" s="34">
+        <v>224855.5</v>
+      </c>
+      <c r="E19" s="31">
+        <v>185.5</v>
+      </c>
       <c r="F19" s="31"/>
       <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
+      <c r="H19" s="34">
+        <v>224670</v>
+      </c>
       <c r="I19" s="31"/>
       <c r="J19" s="31"/>
       <c r="K19" s="31"/>
@@ -2147,15 +2163,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1588398.5</v>
+        <v>2135825.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1362470.5</v>
+        <v>1837105.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>2722.5</v>
+        <v>3259.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2167,7 +2183,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1359866</v>
+        <v>1833964</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -6724,12 +6740,22 @@
       <c r="B18" s="27">
         <v>46182</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
+      <c r="C18" s="32">
+        <v>296582</v>
+      </c>
+      <c r="D18" s="32">
+        <v>248253.5</v>
+      </c>
+      <c r="E18" s="31">
+        <v>267.5</v>
+      </c>
       <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
+      <c r="G18" s="31">
+        <v>2070</v>
+      </c>
+      <c r="H18" s="32">
+        <v>247986</v>
+      </c>
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
       <c r="K18" s="31"/>
@@ -6752,15 +6778,17 @@
       <c r="B19" s="27">
         <v>46183</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
+      <c r="C19" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="46"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -7418,15 +7446,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1434642</v>
+        <v>1731224</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1214528.5</v>
+        <v>1462782</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>1988</v>
+        <v>2255.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7434,11 +7462,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>8664</v>
+        <v>10734</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1212605</v>
+        <v>1460591</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11449,7 +11477,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C15:K15"/>
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C23:K23"/>
@@ -11457,6 +11485,7 @@
     <mergeCell ref="C22:K22"/>
     <mergeCell ref="C30:K30"/>
     <mergeCell ref="C37:K37"/>
+    <mergeCell ref="C19:K19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -11996,12 +12025,22 @@
       <c r="B18" s="27">
         <v>46182</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
+      <c r="C18" s="34">
+        <v>494155</v>
+      </c>
+      <c r="D18" s="32">
+        <v>423587.5</v>
+      </c>
+      <c r="E18" s="31">
+        <v>16.5</v>
+      </c>
       <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
+      <c r="G18" s="31">
+        <v>3288</v>
+      </c>
+      <c r="H18" s="32">
+        <v>423571</v>
+      </c>
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
       <c r="K18" s="31"/>
@@ -12024,12 +12063,22 @@
       <c r="B19" s="27">
         <v>46183</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
+      <c r="C19" s="34">
+        <v>297741</v>
+      </c>
+      <c r="D19" s="34">
+        <v>254515.5</v>
+      </c>
+      <c r="E19" s="31">
+        <v>575.5</v>
+      </c>
       <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
+      <c r="G19" s="31">
+        <v>1296</v>
+      </c>
+      <c r="H19" s="34">
+        <v>253940</v>
+      </c>
       <c r="I19" s="31"/>
       <c r="J19" s="31"/>
       <c r="K19" s="31"/>
@@ -12690,15 +12739,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1999059</v>
+        <v>2790955</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1662585.25</v>
+        <v>2340688.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>15334.25</v>
+        <v>15926.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -12706,11 +12755,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>6810</v>
+        <v>11394</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1647251</v>
+        <v>2324762</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710396EA-2F0B-4852-8B0B-C8799F5BFC12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7416AB31-3516-4222-B8D6-A43E6E224D75}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -147,8 +147,43 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{25751F20-122E-4471-B3E9-0CBFBFBE6EBA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+SI NO. 10938</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="23">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1525,15 +1560,17 @@
       <c r="B20" s="27">
         <v>46184</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
+      <c r="C20" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="46"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -6194,7 +6231,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C30:K30"/>
     <mergeCell ref="C37:K37"/>
@@ -6203,6 +6240,7 @@
     <mergeCell ref="C22:K22"/>
     <mergeCell ref="C23:K23"/>
     <mergeCell ref="C17:K17"/>
+    <mergeCell ref="C20:K20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6808,12 +6846,22 @@
       <c r="B20" s="27">
         <v>46184</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="31"/>
+      <c r="C20" s="32">
+        <v>286866</v>
+      </c>
+      <c r="D20" s="32">
+        <v>243759</v>
+      </c>
+      <c r="E20" s="31">
+        <v>259</v>
+      </c>
       <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
+      <c r="G20" s="34">
+        <v>1932</v>
+      </c>
+      <c r="H20" s="34">
+        <v>243500</v>
+      </c>
       <c r="I20" s="34"/>
       <c r="J20" s="34"/>
       <c r="K20" s="34"/>
@@ -7446,15 +7494,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1731224</v>
+        <v>2018090</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1462782</v>
+        <v>1706541</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>2255.5</v>
+        <v>2514.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7462,11 +7510,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>10734</v>
+        <v>12666</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1460591</v>
+        <v>1704091</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11493,7 +11541,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E737051-E669-4C2F-B4D4-F8B394C392B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E737051-E669-4C2F-B4D4-F8B394C392B3}">
   <dimension ref="A1:V279"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -12101,15 +12149,29 @@
       <c r="B20" s="27">
         <v>46184</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
+      <c r="C20" s="32">
+        <v>291580</v>
+      </c>
+      <c r="D20" s="32">
+        <v>211400.5</v>
+      </c>
       <c r="E20" s="31"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
+      <c r="F20" s="34">
+        <v>7141.5</v>
+      </c>
+      <c r="G20" s="31">
+        <v>1242</v>
+      </c>
+      <c r="H20" s="34">
+        <v>218542</v>
+      </c>
+      <c r="I20" s="31">
+        <v>35098</v>
+      </c>
       <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
+      <c r="K20" s="34">
+        <v>50</v>
+      </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -12739,11 +12801,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2790955</v>
+        <v>3082535</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2340688.25</v>
+        <v>2552088.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -12751,19 +12813,19 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7141.5</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>11394</v>
+        <v>12636</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2324762</v>
+        <v>2543304</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>0</v>
+        <v>35098</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
@@ -12771,7 +12833,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -16781,6 +16843,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7416AB31-3516-4222-B8D6-A43E6E224D75}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88670619-EEBB-4674-A79B-5B78D1FF34B3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JUNE, SRS R1" sheetId="6" r:id="rId1"/>
@@ -143,6 +143,56 @@
         </r>
       </text>
     </comment>
+    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{47571E67-2407-454F-B2DA-49E9E464DF84}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+JONTHAN CENAS
+SI NO. 10941</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J22" authorId="0" shapeId="0" xr:uid="{70424F86-D89D-4272-A5BF-7063AE01EB21}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+JONATHAN CENAS
+SI NO. 10941</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -183,7 +233,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="23">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1590,13 +1640,25 @@
       <c r="B21" s="27">
         <v>46185</v>
       </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="31"/>
+      <c r="C21" s="32">
+        <v>410353</v>
+      </c>
+      <c r="D21" s="32">
+        <v>245949.5</v>
+      </c>
+      <c r="E21" s="31">
+        <v>334.5</v>
+      </c>
       <c r="F21" s="34"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="31"/>
+      <c r="G21" s="31">
+        <v>1074</v>
+      </c>
+      <c r="H21" s="34">
+        <v>245615</v>
+      </c>
+      <c r="I21" s="31">
+        <v>123065</v>
+      </c>
       <c r="J21" s="34"/>
       <c r="K21" s="34"/>
       <c r="L21" s="1"/>
@@ -1618,15 +1680,19 @@
       <c r="B22" s="27">
         <v>46186</v>
       </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="46"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32">
+        <v>123065</v>
+      </c>
+      <c r="E22" s="31"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="34">
+        <v>123065</v>
+      </c>
+      <c r="K22" s="34"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -2200,15 +2266,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2135825.5</v>
+        <v>2546178.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1837105.5</v>
+        <v>2206120</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>3259.5</v>
+        <v>3594</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2216,19 +2282,19 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>7788</v>
+        <v>8862</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1833964</v>
+        <v>2079579</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>150821</v>
+        <v>273886</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>209285</v>
+        <v>332350</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
@@ -6231,13 +6297,12 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C30:K30"/>
     <mergeCell ref="C37:K37"/>
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C16:K16"/>
-    <mergeCell ref="C22:K22"/>
     <mergeCell ref="C23:K23"/>
     <mergeCell ref="C17:K17"/>
     <mergeCell ref="C20:K20"/>
@@ -6856,7 +6921,7 @@
         <v>259</v>
       </c>
       <c r="F20" s="34"/>
-      <c r="G20" s="34">
+      <c r="G20" s="31">
         <v>1932</v>
       </c>
       <c r="H20" s="34">
@@ -6884,12 +6949,22 @@
       <c r="B21" s="27">
         <v>46185</v>
       </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="31"/>
+      <c r="C21" s="32">
+        <v>273580</v>
+      </c>
+      <c r="D21" s="32">
+        <v>226270</v>
+      </c>
+      <c r="E21" s="31">
+        <v>273</v>
+      </c>
       <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
+      <c r="G21" s="31">
+        <v>1140</v>
+      </c>
+      <c r="H21" s="34">
+        <v>225997</v>
+      </c>
       <c r="I21" s="34"/>
       <c r="J21" s="34"/>
       <c r="K21" s="34"/>
@@ -6912,7 +6987,9 @@
       <c r="B22" s="27">
         <v>46186</v>
       </c>
-      <c r="C22" s="44"/>
+      <c r="C22" s="44" t="s">
+        <v>22</v>
+      </c>
       <c r="D22" s="45"/>
       <c r="E22" s="45"/>
       <c r="F22" s="45"/>
@@ -7494,15 +7571,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2018090</v>
+        <v>2291670</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1706541</v>
+        <v>1932811</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>2514.5</v>
+        <v>2787.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7510,11 +7587,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>12666</v>
+        <v>13806</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1704091</v>
+        <v>1930088</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12219,7 +12296,9 @@
       <c r="B22" s="27">
         <v>46186</v>
       </c>
-      <c r="C22" s="44"/>
+      <c r="C22" s="44" t="s">
+        <v>22</v>
+      </c>
       <c r="D22" s="45"/>
       <c r="E22" s="45"/>
       <c r="F22" s="45"/>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88670619-EEBB-4674-A79B-5B78D1FF34B3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8952402-BD58-405F-937D-32CB0A2C2E4A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1742,12 +1742,22 @@
       <c r="B24" s="27">
         <v>46188</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="31"/>
+      <c r="C24" s="32">
+        <v>337138</v>
+      </c>
+      <c r="D24" s="32">
+        <v>301661.90999999997</v>
+      </c>
+      <c r="E24" s="31">
+        <v>713.91</v>
+      </c>
       <c r="F24" s="34"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="34"/>
+      <c r="G24" s="31">
+        <v>2430</v>
+      </c>
+      <c r="H24" s="34">
+        <v>300948</v>
+      </c>
       <c r="I24" s="31"/>
       <c r="J24" s="34"/>
       <c r="K24" s="34"/>
@@ -2266,15 +2276,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2546178.5</v>
+        <v>2883316.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2206120</v>
+        <v>2507781.91</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>3594</v>
+        <v>4307.91</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2282,11 +2292,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>8862</v>
+        <v>11292</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2079579</v>
+        <v>2380527</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -7047,12 +7057,22 @@
       <c r="B24" s="27">
         <v>46188</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
+      <c r="C24" s="32">
+        <v>301187</v>
+      </c>
+      <c r="D24" s="32">
+        <v>253769</v>
+      </c>
       <c r="E24" s="31"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
+      <c r="F24" s="34">
+        <v>25</v>
+      </c>
+      <c r="G24" s="31">
+        <v>2316</v>
+      </c>
+      <c r="H24" s="34">
+        <v>253794</v>
+      </c>
       <c r="I24" s="34"/>
       <c r="J24" s="34"/>
       <c r="K24" s="34"/>
@@ -7571,11 +7591,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2291670</v>
+        <v>2592857</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1932811</v>
+        <v>2186580</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -7583,15 +7603,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>62.5</v>
+        <v>87.5</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>13806</v>
+        <v>16122</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1930088</v>
+        <v>2183882</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12356,15 +12376,25 @@
       <c r="B24" s="27">
         <v>46188</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
+      <c r="C24" s="32">
+        <v>510083</v>
+      </c>
+      <c r="D24" s="32">
+        <v>456901.5</v>
+      </c>
       <c r="E24" s="31"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
+      <c r="F24" s="34">
+        <v>29.5</v>
+      </c>
+      <c r="G24" s="34">
+        <v>1554</v>
+      </c>
       <c r="H24" s="34"/>
       <c r="I24" s="34"/>
       <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
+      <c r="K24" s="34">
+        <v>50</v>
+      </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="7"/>
@@ -12880,11 +12910,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3082535</v>
+        <v>3592618</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2552088.75</v>
+        <v>3008990.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -12892,11 +12922,11 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>7141.5</v>
+        <v>7171</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>12636</v>
+        <v>14190</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
@@ -12912,7 +12942,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8952402-BD58-405F-937D-32CB0A2C2E4A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC00BFD-027E-4E4A-BFA5-44B163374C12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JUNE, SRS R1" sheetId="6" r:id="rId1"/>
@@ -190,6 +190,33 @@
           <t xml:space="preserve">
 JONATHAN CENAS
 SI NO. 10941</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{792B610C-9682-4CA9-B70C-97DDC294CA77}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+DANYEN STORE
+SI NO. 11001
+BALWARTE
+SI NO. 10950</t>
         </r>
       </text>
     </comment>
@@ -1780,14 +1807,30 @@
       <c r="B25" s="27">
         <v>46189</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
+      <c r="C25" s="32">
+        <v>550495</v>
+      </c>
+      <c r="D25" s="32">
+        <v>178173.5</v>
+      </c>
+      <c r="E25" s="31">
+        <v>983.5</v>
+      </c>
       <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
+      <c r="G25" s="31">
+        <v>2592</v>
+      </c>
+      <c r="H25" s="32">
+        <v>177190</v>
+      </c>
+      <c r="I25" s="31">
+        <f>261949+93725</f>
+        <v>355674</v>
+      </c>
+      <c r="J25" s="32">
+        <f>88549</f>
+        <v>88549</v>
+      </c>
       <c r="K25" s="31"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -1808,8 +1851,8 @@
       <c r="B26" s="27">
         <v>46190</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
       <c r="G26" s="31"/>
@@ -2276,15 +2319,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2883316.5</v>
+        <v>3433811.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2507781.91</v>
+        <v>2685955.41</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>4307.91</v>
+        <v>5291.41</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2292,19 +2335,19 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>11292</v>
+        <v>13884</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2380527</v>
+        <v>2557717</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>273886</v>
+        <v>629560</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>332350</v>
+        <v>420899</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
@@ -7095,12 +7138,22 @@
       <c r="B25" s="27">
         <v>46189</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
+      <c r="C25" s="32">
+        <v>252546</v>
+      </c>
+      <c r="D25" s="32">
+        <v>213315</v>
+      </c>
       <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
+      <c r="F25" s="32">
+        <v>412</v>
+      </c>
+      <c r="G25" s="31">
+        <v>1332</v>
+      </c>
+      <c r="H25" s="32">
+        <v>213727</v>
+      </c>
       <c r="I25" s="31"/>
       <c r="J25" s="31"/>
       <c r="K25" s="31"/>
@@ -7591,11 +7644,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2592857</v>
+        <v>2845403</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2186580</v>
+        <v>2399895</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -7603,15 +7656,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>87.5</v>
+        <v>499.5</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>16122</v>
+        <v>17454</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2183882</v>
+        <v>2397609</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12414,12 +12467,22 @@
       <c r="B25" s="27">
         <v>46189</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
+      <c r="C25" s="32">
+        <v>586130</v>
+      </c>
+      <c r="D25" s="32">
+        <v>498151.25</v>
+      </c>
       <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
+      <c r="F25" s="32">
+        <v>1015.75</v>
+      </c>
+      <c r="G25" s="31">
+        <v>2016</v>
+      </c>
+      <c r="H25" s="32">
+        <v>499167</v>
+      </c>
       <c r="I25" s="31"/>
       <c r="J25" s="31"/>
       <c r="K25" s="31"/>
@@ -12443,7 +12506,7 @@
         <v>46190</v>
       </c>
       <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
+      <c r="D26" s="32"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
       <c r="G26" s="31"/>
@@ -12910,11 +12973,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3592618</v>
+        <v>4178748</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3008990.25</v>
+        <v>3507141.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -12922,15 +12985,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>7171</v>
+        <v>8186.75</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>14190</v>
+        <v>16206</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2543304</v>
+        <v>3042471</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC00BFD-027E-4E4A-BFA5-44B163374C12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CE7AC4-E2C4-4E1E-AB58-870D1C0281DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -52,7 +52,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -61,7 +61,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 SOUND CHECK</t>
@@ -151,7 +151,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -160,7 +160,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 JONTHAN CENAS
@@ -176,7 +176,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -185,7 +185,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 JONATHAN CENAS
@@ -201,7 +201,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -210,7 +210,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 DANYEN STORE
@@ -378,7 +378,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,19 +477,6 @@
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1851,12 +1838,20 @@
       <c r="B26" s="27">
         <v>46190</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="31"/>
+      <c r="C26" s="32">
+        <v>265398</v>
+      </c>
+      <c r="D26" s="32">
+        <v>226929.75</v>
+      </c>
+      <c r="E26" s="31">
+        <v>276.75</v>
+      </c>
       <c r="F26" s="31"/>
       <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
+      <c r="H26" s="32">
+        <v>226653</v>
+      </c>
       <c r="I26" s="31"/>
       <c r="J26" s="31"/>
       <c r="K26" s="31"/>
@@ -2319,15 +2314,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3433811.5</v>
+        <v>3699209.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2685955.41</v>
+        <v>2912885.16</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>5291.41</v>
+        <v>5568.16</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2339,7 +2334,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2557717</v>
+        <v>2784370</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -7176,12 +7171,22 @@
       <c r="B26" s="27">
         <v>46190</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
+      <c r="C26" s="32">
+        <v>238898.5</v>
+      </c>
+      <c r="D26" s="32">
+        <v>202771</v>
+      </c>
+      <c r="E26" s="31">
+        <v>252</v>
+      </c>
       <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
+      <c r="G26" s="31">
+        <v>1296</v>
+      </c>
+      <c r="H26" s="32">
+        <v>202519</v>
+      </c>
       <c r="I26" s="31"/>
       <c r="J26" s="31"/>
       <c r="K26" s="31"/>
@@ -7644,15 +7649,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2845403</v>
+        <v>3084301.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2399895</v>
+        <v>2602666</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>2787.5</v>
+        <v>3039.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7660,11 +7665,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>17454</v>
+        <v>18750</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2397609</v>
+        <v>2600128</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12505,15 +12510,27 @@
       <c r="B26" s="27">
         <v>46190</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="31"/>
+      <c r="C26" s="32">
+        <v>403382</v>
+      </c>
+      <c r="D26" s="32">
+        <v>341730</v>
+      </c>
+      <c r="E26" s="31">
+        <v>3084</v>
+      </c>
       <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
+      <c r="G26" s="31">
+        <v>2118</v>
+      </c>
+      <c r="H26" s="32">
+        <v>338646</v>
+      </c>
       <c r="I26" s="31"/>
       <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
+      <c r="K26" s="32">
+        <v>50</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="17"/>
@@ -12973,15 +12990,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4178748</v>
+        <v>4582130</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3507141.5</v>
+        <v>3848871.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>15926.25</v>
+        <v>19010.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -12989,11 +13006,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>16206</v>
+        <v>18324</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3042471</v>
+        <v>3381117</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -13005,7 +13022,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CE7AC4-E2C4-4E1E-AB58-870D1C0281DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4172E703-E688-4A17-899A-6A0274B5F3F0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -220,6 +220,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{9823541A-285D-4B03-AE50-3B4F09BBAC21}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+SI NO. 11015</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -378,7 +403,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -490,6 +515,19 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1874,13 +1912,25 @@
       <c r="B27" s="27">
         <v>46191</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="13"/>
+      <c r="C27" s="11">
+        <v>407264</v>
+      </c>
+      <c r="D27" s="37">
+        <v>272148.25</v>
+      </c>
+      <c r="E27" s="13">
+        <v>507.25</v>
+      </c>
       <c r="F27" s="11"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="43"/>
+      <c r="G27" s="43">
+        <v>1296</v>
+      </c>
+      <c r="H27" s="33">
+        <v>271641</v>
+      </c>
+      <c r="I27" s="43">
+        <v>68110</v>
+      </c>
       <c r="J27" s="33"/>
       <c r="K27" s="30"/>
       <c r="L27" s="1"/>
@@ -2314,15 +2364,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3699209.5</v>
+        <v>4106473.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2912885.16</v>
+        <v>3185033.41</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>5568.16</v>
+        <v>6075.41</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2330,15 +2380,15 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>13884</v>
+        <v>15180</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2784370</v>
+        <v>3056011</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>629560</v>
+        <v>697670</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
@@ -7209,12 +7259,22 @@
       <c r="B27" s="27">
         <v>46191</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="13"/>
+      <c r="C27" s="11">
+        <v>2300743</v>
+      </c>
+      <c r="D27" s="37">
+        <v>196904.5</v>
+      </c>
+      <c r="E27" s="13">
+        <v>47.5</v>
+      </c>
       <c r="F27" s="11"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
+      <c r="G27" s="43">
+        <v>1092</v>
+      </c>
+      <c r="H27" s="33">
+        <v>196857</v>
+      </c>
       <c r="I27" s="33"/>
       <c r="J27" s="33"/>
       <c r="K27" s="30"/>
@@ -7649,15 +7709,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3084301.5</v>
+        <v>5385044.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2602666</v>
+        <v>2799570.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>3039.5</v>
+        <v>3087</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7665,11 +7725,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>18750</v>
+        <v>19842</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2600128</v>
+        <v>2796985</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12550,12 +12610,22 @@
       <c r="B27" s="27">
         <v>46191</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="37"/>
+      <c r="C27" s="11">
+        <v>403373</v>
+      </c>
+      <c r="D27" s="37">
+        <v>333081.5</v>
+      </c>
       <c r="E27" s="13"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
+      <c r="F27" s="11">
+        <v>1495.5</v>
+      </c>
+      <c r="G27" s="43">
+        <v>2910</v>
+      </c>
+      <c r="H27" s="33">
+        <v>334577</v>
+      </c>
       <c r="I27" s="33"/>
       <c r="J27" s="33"/>
       <c r="K27" s="30"/>
@@ -12990,11 +13060,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4582130</v>
+        <v>4985503</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3848871.5</v>
+        <v>4181953</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -13002,15 +13072,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>8186.75</v>
+        <v>9682.25</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>18324</v>
+        <v>21234</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3381117</v>
+        <v>3715694</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4172E703-E688-4A17-899A-6A0274B5F3F0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94516D06-57FB-41CA-89B7-EBEDF078CDB1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="420" windowWidth="29040" windowHeight="15900" activeTab="1" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JUNE, SRS R1" sheetId="6" r:id="rId1"/>
@@ -245,6 +245,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="J28" authorId="0" shapeId="0" xr:uid="{F9DF04CC-819C-44D3-990E-F5C06D90BB1F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+DANYEN
+SI NO. 11001</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -285,7 +310,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="23">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1953,13 +1978,19 @@
         <v>46192</v>
       </c>
       <c r="C28" s="11"/>
-      <c r="D28" s="37"/>
+      <c r="D28" s="37">
+        <v>261949</v>
+      </c>
       <c r="E28" s="13"/>
       <c r="F28" s="11"/>
       <c r="G28" s="43"/>
-      <c r="H28" s="33"/>
+      <c r="H28" s="33">
+        <v>261949</v>
+      </c>
       <c r="I28" s="43"/>
-      <c r="J28" s="33"/>
+      <c r="J28" s="33">
+        <v>261949</v>
+      </c>
       <c r="K28" s="30"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -1980,15 +2011,17 @@
       <c r="B29" s="27">
         <v>46193</v>
       </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="30"/>
+      <c r="C29" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="46"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="7"/>
@@ -2368,7 +2401,7 @@
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3185033.41</v>
+        <v>3446982.41</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -2384,7 +2417,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3056011</v>
+        <v>3317960</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -2392,7 +2425,7 @@
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>420899</v>
+        <v>682848</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
@@ -6395,7 +6428,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C30:K30"/>
     <mergeCell ref="C37:K37"/>
@@ -6404,6 +6437,7 @@
     <mergeCell ref="C23:K23"/>
     <mergeCell ref="C17:K17"/>
     <mergeCell ref="C20:K20"/>
+    <mergeCell ref="C29:K29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -7297,12 +7331,22 @@
       <c r="B28" s="27">
         <v>46192</v>
       </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="13"/>
+      <c r="C28" s="11">
+        <v>251255</v>
+      </c>
+      <c r="D28" s="37">
+        <v>216049.25</v>
+      </c>
+      <c r="E28" s="13">
+        <v>761.25</v>
+      </c>
       <c r="F28" s="11"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
+      <c r="G28" s="43">
+        <v>648</v>
+      </c>
+      <c r="H28" s="33">
+        <v>215288</v>
+      </c>
       <c r="I28" s="33"/>
       <c r="J28" s="33"/>
       <c r="K28" s="30"/>
@@ -7325,15 +7369,17 @@
       <c r="B29" s="27">
         <v>46193</v>
       </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="30"/>
+      <c r="C29" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="46"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="7"/>
@@ -7709,15 +7755,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5385044.5</v>
+        <v>5636299.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2799570.5</v>
+        <v>3015619.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>3087</v>
+        <v>3848.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7725,11 +7771,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>19842</v>
+        <v>20490</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2796985</v>
+        <v>3012273</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11740,7 +11786,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C15:K15"/>
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C23:K23"/>
@@ -11749,6 +11795,7 @@
     <mergeCell ref="C30:K30"/>
     <mergeCell ref="C37:K37"/>
     <mergeCell ref="C19:K19"/>
+    <mergeCell ref="C29:K29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -12504,7 +12551,7 @@
       <c r="F24" s="34">
         <v>29.5</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="31">
         <v>1554</v>
       </c>
       <c r="H24" s="34"/>
@@ -12648,12 +12695,23 @@
       <c r="B28" s="27">
         <v>46192</v>
       </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="37"/>
+      <c r="C28" s="11">
+        <v>327175</v>
+      </c>
+      <c r="D28" s="37">
+        <v>274885</v>
+      </c>
       <c r="E28" s="13"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
+      <c r="F28" s="11">
+        <v>735</v>
+      </c>
+      <c r="G28" s="43">
+        <f>2118</f>
+        <v>2118</v>
+      </c>
+      <c r="H28" s="33">
+        <v>275620</v>
+      </c>
       <c r="I28" s="33"/>
       <c r="J28" s="33"/>
       <c r="K28" s="30"/>
@@ -12676,15 +12734,17 @@
       <c r="B29" s="27">
         <v>46193</v>
       </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="30"/>
+      <c r="C29" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="46"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="7"/>
@@ -13060,11 +13120,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4985503</v>
+        <v>5312678</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4181953</v>
+        <v>4456838</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -13072,15 +13132,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>9682.25</v>
+        <v>10417.25</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>21234</v>
+        <v>23352</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3715694</v>
+        <v>3991314</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -17091,7 +17151,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C22:K22"/>
     <mergeCell ref="C15:K15"/>
@@ -17099,6 +17159,7 @@
     <mergeCell ref="C23:K23"/>
     <mergeCell ref="C30:K30"/>
     <mergeCell ref="C37:K37"/>
+    <mergeCell ref="C29:K29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94516D06-57FB-41CA-89B7-EBEDF078CDB1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2DE0E8-CAE8-453D-9D51-E5EB0F347074}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="420" windowWidth="29040" windowHeight="15900" activeTab="1" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JUNE, SRS R1" sheetId="6" r:id="rId1"/>
@@ -2071,12 +2071,22 @@
       <c r="B31" s="27">
         <v>46195</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="13"/>
+      <c r="C31" s="11">
+        <v>302668</v>
+      </c>
+      <c r="D31" s="37">
+        <v>255001</v>
+      </c>
+      <c r="E31" s="13">
+        <v>171</v>
+      </c>
       <c r="F31" s="11"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="33"/>
+      <c r="G31" s="43">
+        <v>1728</v>
+      </c>
+      <c r="H31" s="33">
+        <v>254830</v>
+      </c>
       <c r="I31" s="43"/>
       <c r="J31" s="33"/>
       <c r="K31" s="30"/>
@@ -2397,15 +2407,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4106473.5</v>
+        <v>4409141.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3446982.41</v>
+        <v>3701983.41</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>6075.41</v>
+        <v>6246.41</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2413,11 +2423,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>15180</v>
+        <v>16908</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3317960</v>
+        <v>3572790</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -7429,12 +7439,22 @@
       <c r="B31" s="27">
         <v>46195</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="13"/>
+      <c r="C31" s="11">
+        <v>262664</v>
+      </c>
+      <c r="D31" s="37">
+        <v>223891.25</v>
+      </c>
+      <c r="E31" s="13">
+        <v>16.25</v>
+      </c>
       <c r="F31" s="11"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
+      <c r="G31" s="43">
+        <v>1296</v>
+      </c>
+      <c r="H31" s="33">
+        <v>223875</v>
+      </c>
       <c r="I31" s="33"/>
       <c r="J31" s="33"/>
       <c r="K31" s="30"/>
@@ -7755,15 +7775,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5636299.5</v>
+        <v>5898963.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3015619.75</v>
+        <v>3239511</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>3848.25</v>
+        <v>3864.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7771,11 +7791,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>20490</v>
+        <v>21786</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3012273</v>
+        <v>3236148</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12794,15 +12814,27 @@
       <c r="B31" s="27">
         <v>46195</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="13"/>
+      <c r="C31" s="11">
+        <v>294801</v>
+      </c>
+      <c r="D31" s="37">
+        <v>255121</v>
+      </c>
+      <c r="E31" s="13">
+        <v>3959</v>
+      </c>
       <c r="F31" s="11"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
+      <c r="G31" s="43">
+        <v>1890</v>
+      </c>
+      <c r="H31" s="33">
+        <v>251162</v>
+      </c>
       <c r="I31" s="33"/>
       <c r="J31" s="33"/>
-      <c r="K31" s="30"/>
+      <c r="K31" s="30">
+        <v>50</v>
+      </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="17"/>
@@ -13120,15 +13152,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5312678</v>
+        <v>5607479</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4456838</v>
+        <v>4711959</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>19010.25</v>
+        <v>22969.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -13136,11 +13168,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>23352</v>
+        <v>25242</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3991314</v>
+        <v>4242476</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -13152,7 +13184,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2DE0E8-CAE8-453D-9D51-E5EB0F347074}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBC7444-9036-48BE-BD8A-DA7675B34934}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -2109,12 +2109,22 @@
       <c r="B32" s="27">
         <v>46196</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
+      <c r="C32" s="32">
+        <v>379402</v>
+      </c>
+      <c r="D32" s="32">
+        <v>339520</v>
+      </c>
+      <c r="E32" s="31">
+        <v>50</v>
+      </c>
       <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
+      <c r="G32" s="31">
+        <v>2652</v>
+      </c>
+      <c r="H32" s="32">
+        <v>339470</v>
+      </c>
       <c r="I32" s="31"/>
       <c r="J32" s="31"/>
       <c r="K32" s="31"/>
@@ -2407,15 +2417,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4409141.5</v>
+        <v>4788543.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3701983.41</v>
+        <v>4041503.41</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>6246.41</v>
+        <v>6296.41</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2423,11 +2433,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>16908</v>
+        <v>19560</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3572790</v>
+        <v>3912260</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -7477,12 +7487,22 @@
       <c r="B32" s="27">
         <v>46196</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
+      <c r="C32" s="32">
+        <v>231037</v>
+      </c>
+      <c r="D32" s="32">
+        <v>194311</v>
+      </c>
       <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
+      <c r="F32" s="32">
+        <v>223</v>
+      </c>
+      <c r="G32" s="31">
+        <v>1440</v>
+      </c>
+      <c r="H32" s="32">
+        <v>194534</v>
+      </c>
       <c r="I32" s="31"/>
       <c r="J32" s="31"/>
       <c r="K32" s="31"/>
@@ -7775,11 +7795,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5898963.5</v>
+        <v>6130000.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3239511</v>
+        <v>3433822</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -7787,15 +7807,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>499.5</v>
+        <v>722.5</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>21786</v>
+        <v>23226</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3236148</v>
+        <v>3430682</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12854,12 +12874,22 @@
       <c r="B32" s="27">
         <v>46196</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
+      <c r="C32" s="32">
+        <v>570554</v>
+      </c>
+      <c r="D32" s="32">
+        <v>484236.5</v>
+      </c>
       <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
+      <c r="F32" s="32">
+        <v>7626.5</v>
+      </c>
+      <c r="G32" s="31">
+        <v>3240</v>
+      </c>
+      <c r="H32" s="32">
+        <v>491863</v>
+      </c>
       <c r="I32" s="31"/>
       <c r="J32" s="31"/>
       <c r="K32" s="31"/>
@@ -13152,11 +13182,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5607479</v>
+        <v>6178033</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4711959</v>
+        <v>5196195.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -13164,15 +13194,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>10417.25</v>
+        <v>18043.75</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>25242</v>
+        <v>28482</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4242476</v>
+        <v>4734339</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBC7444-9036-48BE-BD8A-DA7675B34934}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB7A92E-F0F5-43D0-A28A-C4198E068673}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB7A92E-F0F5-43D0-A28A-C4198E068673}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26797C8F-5440-4039-BEDB-EE9C0C103612}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JUNE, SRS R1" sheetId="6" r:id="rId1"/>
@@ -2147,12 +2147,20 @@
       <c r="B33" s="27">
         <v>46197</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
+      <c r="C33" s="32">
+        <v>287816</v>
+      </c>
+      <c r="D33" s="32">
+        <v>245066</v>
+      </c>
+      <c r="E33" s="31">
+        <v>350</v>
+      </c>
       <c r="F33" s="31"/>
       <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
+      <c r="H33" s="32">
+        <v>244716</v>
+      </c>
       <c r="I33" s="31"/>
       <c r="J33" s="31"/>
       <c r="K33" s="31"/>
@@ -2417,15 +2425,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4788543.5</v>
+        <v>5076359.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4041503.41</v>
+        <v>4286569.41</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>6296.41</v>
+        <v>6646.41</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2437,7 +2445,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3912260</v>
+        <v>4156976</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -7525,12 +7533,22 @@
       <c r="B33" s="27">
         <v>46197</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
+      <c r="C33" s="32">
+        <v>259093</v>
+      </c>
+      <c r="D33" s="32">
+        <v>218966.5</v>
+      </c>
       <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
+      <c r="F33" s="32">
+        <v>153.5</v>
+      </c>
+      <c r="G33" s="31">
+        <v>1926</v>
+      </c>
+      <c r="H33" s="32">
+        <v>219120</v>
+      </c>
       <c r="I33" s="31"/>
       <c r="J33" s="31"/>
       <c r="K33" s="31"/>
@@ -7795,11 +7813,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6130000.5</v>
+        <v>6389093.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3433822</v>
+        <v>3652788.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -7807,15 +7825,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>722.5</v>
+        <v>876</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>23226</v>
+        <v>25152</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3430682</v>
+        <v>3649802</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12912,15 +12930,27 @@
       <c r="B33" s="27">
         <v>46197</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
+      <c r="C33" s="32">
+        <v>475704</v>
+      </c>
+      <c r="D33" s="32">
+        <v>395488</v>
+      </c>
+      <c r="E33" s="31">
+        <v>617</v>
+      </c>
       <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
+      <c r="G33" s="31">
+        <v>2142</v>
+      </c>
+      <c r="H33" s="32">
+        <v>394871</v>
+      </c>
       <c r="I33" s="31"/>
       <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
+      <c r="K33" s="32">
+        <v>50</v>
+      </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="7"/>
@@ -13182,15 +13212,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6178033</v>
+        <v>6653737</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>5196195.5</v>
+        <v>5591683.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>22969.25</v>
+        <v>23586.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -13198,11 +13228,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>28482</v>
+        <v>30624</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4734339</v>
+        <v>5129210</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -13214,7 +13244,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26797C8F-5440-4039-BEDB-EE9C0C103612}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6989D3E-3825-4D83-B8DD-BE83C6DE2DB0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -267,6 +267,32 @@
           <t xml:space="preserve">
 DANYEN
 SI NO. 11001</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I34" authorId="0" shapeId="0" xr:uid="{35D9FC90-7438-4F1D-A3C4-FFDAC6DEC29B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+S.I NO 11174
+</t>
         </r>
       </text>
     </comment>
@@ -2183,13 +2209,23 @@
       <c r="B34" s="27">
         <v>46198</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="40"/>
+      <c r="C34" s="24">
+        <v>452512</v>
+      </c>
+      <c r="D34" s="24">
+        <v>327209</v>
+      </c>
+      <c r="E34" s="40">
+        <v>2190</v>
+      </c>
       <c r="F34" s="11"/>
       <c r="G34" s="40"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="40"/>
+      <c r="H34" s="11">
+        <v>325019</v>
+      </c>
+      <c r="I34" s="40">
+        <v>58202</v>
+      </c>
       <c r="J34" s="11"/>
       <c r="K34" s="34"/>
       <c r="L34" s="1"/>
@@ -2425,15 +2461,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5076359.5</v>
+        <v>5528871.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4286569.41</v>
+        <v>4613778.41</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>6646.41</v>
+        <v>8836.41</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2445,11 +2481,11 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4156976</v>
+        <v>4481995</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>697670</v>
+        <v>755872</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
@@ -7571,12 +7607,20 @@
       <c r="B34" s="27">
         <v>46198</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="40"/>
+      <c r="C34" s="24">
+        <v>234047</v>
+      </c>
+      <c r="D34" s="24">
+        <v>201350.75</v>
+      </c>
+      <c r="E34" s="40">
+        <v>350.75</v>
+      </c>
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
+      <c r="H34" s="11">
+        <v>201000</v>
+      </c>
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
       <c r="K34" s="34"/>
@@ -7813,15 +7857,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6389093.5</v>
+        <v>6623140.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3652788.5</v>
+        <v>3854139.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>3864.5</v>
+        <v>4215.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7833,7 +7877,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3649802</v>
+        <v>3850802</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12970,12 +13014,22 @@
       <c r="B34" s="27">
         <v>46198</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="40"/>
+      <c r="C34" s="32">
+        <v>398637</v>
+      </c>
+      <c r="D34" s="32">
+        <v>344877</v>
+      </c>
+      <c r="E34" s="40">
+        <v>6089</v>
+      </c>
       <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
+      <c r="G34" s="40">
+        <v>648</v>
+      </c>
+      <c r="H34" s="11">
+        <v>338788</v>
+      </c>
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
       <c r="K34" s="34"/>
@@ -13212,15 +13266,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6653737</v>
+        <v>7052374</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>5591683.5</v>
+        <v>5936560.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>23586.25</v>
+        <v>29675.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -13228,11 +13282,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>30624</v>
+        <v>31272</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>5129210</v>
+        <v>5467998</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6989D3E-3825-4D83-B8DD-BE83C6DE2DB0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB62D67E-37EB-40FE-B9FB-C1C03B6DDCA0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JUNE, SRS R1" sheetId="6" r:id="rId1"/>
@@ -7643,12 +7643,22 @@
       <c r="B35" s="27">
         <v>46199</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
+      <c r="C35" s="32">
+        <v>384839</v>
+      </c>
+      <c r="D35" s="24">
+        <v>335375.75</v>
+      </c>
       <c r="E35" s="40"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
+      <c r="F35" s="11">
+        <v>1521</v>
+      </c>
+      <c r="G35" s="40">
+        <v>2244</v>
+      </c>
+      <c r="H35" s="11">
+        <v>336897</v>
+      </c>
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
       <c r="K35" s="34"/>
@@ -7857,11 +7867,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6623140.5</v>
+        <v>7007979.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3854139.25</v>
+        <v>4189515</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -7869,15 +7879,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>876</v>
+        <v>2397</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>25152</v>
+        <v>27396</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3850802</v>
+        <v>4187699</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -13052,12 +13062,20 @@
       <c r="B35" s="27">
         <v>46199</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
+      <c r="C35" s="32">
+        <v>296303</v>
+      </c>
+      <c r="D35" s="32">
+        <v>267421.25</v>
+      </c>
       <c r="E35" s="40"/>
-      <c r="F35" s="11"/>
+      <c r="F35" s="11">
+        <v>6401.75</v>
+      </c>
       <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
+      <c r="H35" s="11">
+        <v>273823</v>
+      </c>
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
       <c r="K35" s="34"/>
@@ -13266,11 +13284,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>7052374</v>
+        <v>7348677</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>5936560.5</v>
+        <v>6203981.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -13278,7 +13296,7 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>18043.75</v>
+        <v>24445.5</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
@@ -13286,7 +13304,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>5467998</v>
+        <v>5741821</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB62D67E-37EB-40FE-B9FB-C1C03B6DDCA0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49669555-4B08-4719-B9C0-3700932D15E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JUNE, SRS R1" sheetId="6" r:id="rId1"/>
@@ -271,6 +271,32 @@
       </text>
     </comment>
     <comment ref="I34" authorId="0" shapeId="0" xr:uid="{35D9FC90-7438-4F1D-A3C4-FFDAC6DEC29B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+S.I NO 11174
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J36" authorId="0" shapeId="0" xr:uid="{484F76EB-AA50-4A88-920C-35B0862AB476}">
       <text>
         <r>
           <rPr>
@@ -2282,7 +2308,9 @@
       <c r="G36" s="43"/>
       <c r="H36" s="33"/>
       <c r="I36" s="43"/>
-      <c r="J36" s="33"/>
+      <c r="J36" s="33">
+        <v>58202</v>
+      </c>
       <c r="K36" s="30"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -2489,7 +2517,7 @@
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>682848</v>
+        <v>741050</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49669555-4B08-4719-B9C0-3700932D15E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B1F05B-0C33-47D6-BF7A-8C99676A9A99}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -362,7 +362,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="23">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -2235,12 +2235,10 @@
       <c r="B34" s="27">
         <v>46198</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="32">
         <v>452512</v>
       </c>
-      <c r="D34" s="24">
-        <v>327209</v>
-      </c>
+      <c r="D34" s="32"/>
       <c r="E34" s="40">
         <v>2190</v>
       </c>
@@ -2273,15 +2271,17 @@
       <c r="B35" s="27">
         <v>46199</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="40"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="34"/>
+      <c r="C35" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45"/>
+      <c r="K35" s="46"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="7"/>
@@ -2361,12 +2361,22 @@
       <c r="B38" s="27">
         <v>46202</v>
       </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
+      <c r="C38" s="32">
+        <v>475002</v>
+      </c>
+      <c r="D38" s="32">
+        <v>414459.75</v>
+      </c>
       <c r="E38" s="40"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="11"/>
+      <c r="F38" s="11">
+        <v>1103.25</v>
+      </c>
+      <c r="G38" s="40">
+        <v>3348</v>
+      </c>
+      <c r="H38" s="11">
+        <v>415563</v>
+      </c>
       <c r="I38" s="40"/>
       <c r="J38" s="11"/>
       <c r="K38" s="34"/>
@@ -2389,8 +2399,8 @@
       <c r="B39" s="27">
         <v>46203</v>
       </c>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
       <c r="E39" s="31"/>
       <c r="F39" s="31"/>
       <c r="G39" s="31"/>
@@ -2489,11 +2499,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5528871.5</v>
+        <v>6003873.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4613778.41</v>
+        <v>4701029.16</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -2501,15 +2511,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>1221.25</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>19560</v>
+        <v>22908</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4481995</v>
+        <v>4897558</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -6520,7 +6530,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C30:K30"/>
     <mergeCell ref="C37:K37"/>
@@ -6530,6 +6540,7 @@
     <mergeCell ref="C17:K17"/>
     <mergeCell ref="C20:K20"/>
     <mergeCell ref="C29:K29"/>
+    <mergeCell ref="C35:K35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -7635,10 +7646,10 @@
       <c r="B34" s="27">
         <v>46198</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="32">
         <v>234047</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="32">
         <v>201350.75</v>
       </c>
       <c r="E34" s="40">
@@ -7674,7 +7685,7 @@
       <c r="C35" s="32">
         <v>384839</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="32">
         <v>335375.75</v>
       </c>
       <c r="E35" s="40"/>
@@ -7767,12 +7778,22 @@
       <c r="B38" s="27">
         <v>46202</v>
       </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="40"/>
+      <c r="C38" s="32">
+        <v>232541.5</v>
+      </c>
+      <c r="D38" s="32">
+        <v>197559.25</v>
+      </c>
+      <c r="E38" s="40">
+        <v>1696.25</v>
+      </c>
       <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
+      <c r="G38" s="40">
+        <v>810</v>
+      </c>
+      <c r="H38" s="11">
+        <v>195863</v>
+      </c>
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
       <c r="K38" s="34"/>
@@ -7895,15 +7916,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>7007979.5</v>
+        <v>7240521</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4189515</v>
+        <v>4387074.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>4215.25</v>
+        <v>5911.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7911,11 +7932,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>27396</v>
+        <v>28206</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4187699</v>
+        <v>4383562</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -13184,12 +13205,22 @@
       <c r="B38" s="27">
         <v>46202</v>
       </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="40"/>
+      <c r="C38" s="32">
+        <v>419626</v>
+      </c>
+      <c r="D38" s="32">
+        <v>356119</v>
+      </c>
+      <c r="E38" s="40">
+        <v>3894</v>
+      </c>
       <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
+      <c r="G38" s="11">
+        <v>2832</v>
+      </c>
+      <c r="H38" s="11">
+        <v>352225</v>
+      </c>
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
       <c r="K38" s="34"/>
@@ -13312,15 +13343,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>7348677</v>
+        <v>7768303</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>6203981.75</v>
+        <v>6560100.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>29675.25</v>
+        <v>33569.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -13328,11 +13359,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>31272</v>
+        <v>34104</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>5741821</v>
+        <v>6094046</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B1F05B-0C33-47D6-BF7A-8C99676A9A99}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E333192-8F84-4849-BE1D-6836855006D4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -318,6 +318,58 @@
           <t xml:space="preserve">
 SOUND CHECK
 S.I NO 11174
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I39" authorId="0" shapeId="0" xr:uid="{C7A43FD8-106A-4940-99D8-F7689F3B2619}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+BALWARTE
+S.I NO 11180
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J39" authorId="0" shapeId="0" xr:uid="{95A2040B-8B60-4EA5-8C52-480A8CA12F53}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+BALWARTE
+S I NO 10950
 </t>
         </r>
       </text>
@@ -2238,7 +2290,9 @@
       <c r="C34" s="32">
         <v>452512</v>
       </c>
-      <c r="D34" s="32"/>
+      <c r="D34" s="32">
+        <v>32729</v>
+      </c>
       <c r="E34" s="40">
         <v>2190</v>
       </c>
@@ -2399,14 +2453,28 @@
       <c r="B39" s="27">
         <v>46203</v>
       </c>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="31"/>
+      <c r="C39" s="32">
+        <v>393812.5</v>
+      </c>
+      <c r="D39" s="32">
+        <v>345331.5</v>
+      </c>
+      <c r="E39" s="31">
+        <v>89</v>
+      </c>
       <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
+      <c r="G39" s="31">
+        <v>1944</v>
+      </c>
+      <c r="H39" s="34">
+        <v>345242.5</v>
+      </c>
+      <c r="I39" s="31">
+        <v>84261</v>
+      </c>
+      <c r="J39" s="34">
+        <v>93725</v>
+      </c>
       <c r="K39" s="31"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2499,15 +2567,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6003873.5</v>
+        <v>6397686</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4701029.16</v>
+        <v>5079089.66</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>8836.41</v>
+        <v>8925.41</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2515,19 +2583,19 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>22908</v>
+        <v>24852</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4897558</v>
+        <v>5242800.5</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>755872</v>
+        <v>840133</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>741050</v>
+        <v>834775</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
@@ -7816,12 +7884,22 @@
       <c r="B39" s="27">
         <v>46203</v>
       </c>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
+      <c r="C39" s="32">
+        <v>231345</v>
+      </c>
+      <c r="D39" s="32">
+        <v>195222.75</v>
+      </c>
       <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
+      <c r="F39" s="34">
+        <v>218.25</v>
+      </c>
+      <c r="G39" s="31">
+        <v>1110</v>
+      </c>
+      <c r="H39" s="34">
+        <v>195441</v>
+      </c>
       <c r="I39" s="31"/>
       <c r="J39" s="31"/>
       <c r="K39" s="31"/>
@@ -7916,11 +7994,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>7240521</v>
+        <v>7471866</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4387074.25</v>
+        <v>4582297</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -7928,15 +8006,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>2397</v>
+        <v>2615.25</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>28206</v>
+        <v>29316</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4383562</v>
+        <v>4579003</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -13215,7 +13293,7 @@
         <v>3894</v>
       </c>
       <c r="F38" s="11"/>
-      <c r="G38" s="11">
+      <c r="G38" s="40">
         <v>2832</v>
       </c>
       <c r="H38" s="11">
@@ -13243,12 +13321,22 @@
       <c r="B39" s="27">
         <v>46203</v>
       </c>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
+      <c r="C39" s="32">
+        <v>305063</v>
+      </c>
+      <c r="D39" s="32">
+        <v>257049.5</v>
+      </c>
       <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
+      <c r="F39" s="34">
+        <v>4405</v>
+      </c>
+      <c r="G39" s="31">
+        <v>1578</v>
+      </c>
+      <c r="H39" s="34">
+        <v>261454.5</v>
+      </c>
       <c r="I39" s="31"/>
       <c r="J39" s="31"/>
       <c r="K39" s="31"/>
@@ -13343,11 +13431,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>7768303</v>
+        <v>8073366</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>6560100.75</v>
+        <v>6817150.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -13355,15 +13443,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>24445.5</v>
+        <v>28850.5</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>34104</v>
+        <v>35682</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>6094046</v>
+        <v>6355500.5</v>
       </c>
       <c r="I43" s="16">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E333192-8F84-4849-BE1D-6836855006D4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A664D5E9-C7A6-456F-BC14-90937676872A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>

--- a/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
+++ b/GBDS JUNE FILES 2026/SHORT OVER ALL ROUTES - JUNE 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JUNE FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A664D5E9-C7A6-456F-BC14-90937676872A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7A86A7-C38E-4EB9-BBE4-3E85DCB84C99}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
